--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,9 +484,26 @@
         <v>user</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>999</v>
+      </c>
+      <c r="B6" t="str">
+        <v>developer</v>
+      </c>
+      <c r="C6" t="str">
+        <v>dev123</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Developer Account</v>
+      </c>
+      <c r="E6" t="str">
+        <v>developer</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,9 +501,26 @@
         <v>developer</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ramadanawa</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ramgaming03</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Ramadhan</v>
+      </c>
+      <c r="E7" t="str">
+        <v>user</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,16 +452,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="str">
-        <v>rama003</v>
+        <v>abdul123</v>
       </c>
       <c r="C4" t="str">
         <v>ramgaming03</v>
       </c>
       <c r="D4" t="str">
-        <v>rama</v>
+        <v>Abdul Rahman</v>
       </c>
       <c r="E4" t="str">
         <v>user</v>
@@ -469,58 +469,41 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>999</v>
       </c>
       <c r="B5" t="str">
-        <v>abdul123</v>
+        <v>developer</v>
       </c>
       <c r="C5" t="str">
-        <v>ramgaming03</v>
+        <v>dev123</v>
       </c>
       <c r="D5" t="str">
-        <v>Abdul Rahman</v>
+        <v>Developer Account</v>
       </c>
       <c r="E5" t="str">
-        <v>user</v>
+        <v>developer</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B6" t="str">
-        <v>developer</v>
+        <v>ramadanawa</v>
       </c>
       <c r="C6" t="str">
-        <v>dev123</v>
+        <v>ramgaming03</v>
       </c>
       <c r="D6" t="str">
-        <v>Developer Account</v>
+        <v>Ramadhan</v>
       </c>
       <c r="E6" t="str">
-        <v>developer</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ramadanawa</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ramgaming03</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Ramadhan</v>
-      </c>
-      <c r="E7" t="str">
         <v>user</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,58 +452,41 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>4</v>
+        <v>999</v>
       </c>
       <c r="B4" t="str">
-        <v>abdul123</v>
+        <v>developer</v>
       </c>
       <c r="C4" t="str">
-        <v>ramgaming03</v>
+        <v>dev123</v>
       </c>
       <c r="D4" t="str">
-        <v>Abdul Rahman</v>
+        <v>Developer Account</v>
       </c>
       <c r="E4" t="str">
-        <v>user</v>
+        <v>developer</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B5" t="str">
-        <v>developer</v>
+        <v>ramadanawa</v>
       </c>
       <c r="C5" t="str">
-        <v>dev123</v>
+        <v>ramgaming03</v>
       </c>
       <c r="D5" t="str">
-        <v>Developer Account</v>
+        <v>Ramadhan</v>
       </c>
       <c r="E5" t="str">
-        <v>developer</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>1000</v>
-      </c>
-      <c r="B6" t="str">
-        <v>ramadanawa</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ramgaming03</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Ramadhan</v>
-      </c>
-      <c r="E6" t="str">
         <v>user</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,9 +484,26 @@
         <v>user</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>1001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>rama03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ramgaming03</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Rizky Ramadhan</v>
+      </c>
+      <c r="E6" t="str">
+        <v>user</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -489,7 +489,7 @@
         <v>1001</v>
       </c>
       <c r="B6" t="str">
-        <v>rama03</v>
+        <v>rama07</v>
       </c>
       <c r="C6" t="str">
         <v>ramgaming03</v>

--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,9 +501,26 @@
         <v>user</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>1002</v>
+      </c>
+      <c r="B7" t="str">
+        <v>bang_zam</v>
+      </c>
+      <c r="C7" t="str">
+        <v>admin123</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Az6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>user</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,26 +501,9 @@
         <v>user</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7">
-        <v>1002</v>
-      </c>
-      <c r="B7" t="str">
-        <v>bang_zam</v>
-      </c>
-      <c r="C7" t="str">
-        <v>admin123</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Az6</v>
-      </c>
-      <c r="E7" t="str">
-        <v>user</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,26 +484,9 @@
         <v>user</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>1001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>rama07</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ramgaming03</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Rizky Ramadhan</v>
-      </c>
-      <c r="E6" t="str">
-        <v>user</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>